--- a/技术文档/草稿 V1/Book1.xlsx
+++ b/技术文档/草稿 V1/Book1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\Minecraft NB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\Minecaft\MinecraftLittletilesReader\技术文档\草稿 V1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE51AF0E-FC51-4DD2-8F91-AFB925105EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E29E12-E4FE-47D8-BAA6-987CE6EB01D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2DB52894-975B-483F-8B64-E8D4AE6D7204}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="26116" windowHeight="16395" xr2:uid="{2DB52894-975B-483F-8B64-E8D4AE6D7204}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -289,6 +289,12 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -307,6 +313,18 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -317,24 +335,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -944,111 +944,111 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC7EA87B-D05E-4242-9669-DC6DE248F540}">
   <dimension ref="A2:AH37"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="4.36328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="1" customWidth="1"/>
-    <col min="3" max="34" width="4.1796875" style="1" customWidth="1"/>
-    <col min="35" max="16384" width="8.7265625" style="1"/>
+    <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.06640625" style="1" customWidth="1"/>
+    <col min="3" max="34" width="4.19921875" style="1" customWidth="1"/>
+    <col min="35" max="16384" width="8.73046875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="B2" s="6" t="s">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.45">
+      <c r="B2" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="16" t="s">
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="T2" s="16"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="16"/>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="16"/>
-      <c r="AB2" s="16"/>
-      <c r="AC2" s="16"/>
-      <c r="AD2" s="16"/>
-      <c r="AE2" s="16"/>
-      <c r="AF2" s="16"/>
-      <c r="AG2" s="16"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17"/>
+      <c r="V2" s="17"/>
+      <c r="W2" s="17"/>
+      <c r="X2" s="17"/>
+      <c r="Y2" s="17"/>
+      <c r="Z2" s="17"/>
+      <c r="AA2" s="17"/>
+      <c r="AB2" s="17"/>
+      <c r="AC2" s="17"/>
+      <c r="AD2" s="17"/>
+      <c r="AE2" s="17"/>
+      <c r="AF2" s="17"/>
+      <c r="AG2" s="17"/>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.45">
       <c r="A3" s="2"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="15" t="s">
+      <c r="B3" s="9"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15" t="s">
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
-      <c r="P3" s="15" t="s">
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="Q3" s="15"/>
-      <c r="R3" s="15"/>
-      <c r="S3" s="15" t="s">
+      <c r="Q3" s="21"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="T3" s="15"/>
-      <c r="U3" s="15"/>
-      <c r="V3" s="15" t="s">
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="W3" s="15"/>
-      <c r="X3" s="15"/>
-      <c r="Y3" s="15" t="s">
+      <c r="W3" s="21"/>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="Z3" s="15"/>
-      <c r="AA3" s="15"/>
-      <c r="AB3" s="15" t="s">
+      <c r="Z3" s="21"/>
+      <c r="AA3" s="21"/>
+      <c r="AB3" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="AC3" s="15"/>
-      <c r="AD3" s="15"/>
-      <c r="AE3" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF3" s="15"/>
-      <c r="AG3" s="15"/>
+      <c r="AC3" s="21"/>
+      <c r="AD3" s="21"/>
+      <c r="AE3" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="21"/>
+      <c r="AG3" s="21"/>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.45">
       <c r="A4" s="2"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="11"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="13"/>
       <c r="D4" s="3" t="s">
         <v>17</v>
       </c>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="AH4" s="2"/>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.45">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AG5" s="4"/>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.45">
       <c r="B6" s="4">
         <f>B5 * 2^31</f>
         <v>2147483648</v>
@@ -1313,7 +1313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.45">
       <c r="B7" s="5">
         <v>31</v>
       </c>
@@ -1411,13 +1411,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.45">
       <c r="B9" s="1">
         <f>IF(B5=1,-1*(2^31-SUM(C6:AG6)),SUM(C6:AG6))</f>
         <v>-2147483630</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.45">
       <c r="AE11" s="1" t="s">
         <v>0</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.45">
       <c r="AE12" s="1" t="s">
         <v>1</v>
       </c>
@@ -1439,7 +1439,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.45">
       <c r="AE13" s="1" t="s">
         <v>4</v>
       </c>
@@ -1450,7 +1450,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.45">
       <c r="AE14" s="1" t="s">
         <v>5</v>
       </c>
@@ -1461,99 +1461,99 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.35">
-      <c r="B33" s="6" t="s">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.45">
+      <c r="B33" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="9"/>
-      <c r="D33" s="17" t="s">
+      <c r="C33" s="11"/>
+      <c r="D33" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="16" t="s">
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="16"/>
-      <c r="O33" s="16"/>
-      <c r="P33" s="16"/>
-      <c r="Q33" s="16"/>
-      <c r="R33" s="16"/>
-      <c r="S33" s="16"/>
-      <c r="T33" s="16"/>
-      <c r="U33" s="16"/>
-      <c r="V33" s="16"/>
-      <c r="W33" s="16"/>
-      <c r="X33" s="16"/>
-      <c r="Y33" s="16"/>
-      <c r="Z33" s="16"/>
-      <c r="AA33" s="16"/>
-      <c r="AB33" s="16"/>
-      <c r="AC33" s="16"/>
-      <c r="AD33" s="16"/>
-      <c r="AE33" s="16"/>
-      <c r="AF33" s="16"/>
-      <c r="AG33" s="16"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17"/>
+      <c r="M33" s="17"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="17"/>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="17"/>
+      <c r="S33" s="17"/>
+      <c r="T33" s="17"/>
+      <c r="U33" s="17"/>
+      <c r="V33" s="17"/>
+      <c r="W33" s="17"/>
+      <c r="X33" s="17"/>
+      <c r="Y33" s="17"/>
+      <c r="Z33" s="17"/>
+      <c r="AA33" s="17"/>
+      <c r="AB33" s="17"/>
+      <c r="AC33" s="17"/>
+      <c r="AD33" s="17"/>
+      <c r="AE33" s="17"/>
+      <c r="AF33" s="17"/>
+      <c r="AG33" s="17"/>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.35">
-      <c r="B34" s="7"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="15" t="s">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.45">
+      <c r="B34" s="9"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15" t="s">
+      <c r="K34" s="21"/>
+      <c r="L34" s="21"/>
+      <c r="M34" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="N34" s="15"/>
-      <c r="O34" s="15"/>
-      <c r="P34" s="15" t="s">
+      <c r="N34" s="21"/>
+      <c r="O34" s="21"/>
+      <c r="P34" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="Q34" s="15"/>
-      <c r="R34" s="15"/>
-      <c r="S34" s="15" t="s">
+      <c r="Q34" s="21"/>
+      <c r="R34" s="21"/>
+      <c r="S34" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="T34" s="15"/>
-      <c r="U34" s="15"/>
-      <c r="V34" s="15" t="s">
+      <c r="T34" s="21"/>
+      <c r="U34" s="21"/>
+      <c r="V34" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="W34" s="15"/>
-      <c r="X34" s="15"/>
-      <c r="Y34" s="15" t="s">
+      <c r="W34" s="21"/>
+      <c r="X34" s="21"/>
+      <c r="Y34" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="Z34" s="15"/>
-      <c r="AA34" s="15"/>
-      <c r="AB34" s="15" t="s">
+      <c r="Z34" s="21"/>
+      <c r="AA34" s="21"/>
+      <c r="AB34" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="AC34" s="15"/>
-      <c r="AD34" s="15"/>
-      <c r="AE34" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF34" s="15"/>
-      <c r="AG34" s="15"/>
+      <c r="AC34" s="21"/>
+      <c r="AD34" s="21"/>
+      <c r="AE34" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="21"/>
+      <c r="AG34" s="21"/>
     </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.35">
-      <c r="B35" s="8"/>
-      <c r="C35" s="11"/>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.45">
+      <c r="B35" s="10"/>
+      <c r="C35" s="13"/>
       <c r="D35" s="3" t="s">
         <v>17</v>
       </c>
@@ -1629,7 +1629,7 @@
       <c r="AB35" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AC35" s="21" t="s">
+      <c r="AC35" s="7" t="s">
         <v>10</v>
       </c>
       <c r="AD35" s="3" t="s">
@@ -1638,14 +1638,14 @@
       <c r="AE35" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AF35" s="21" t="s">
+      <c r="AF35" s="7" t="s">
         <v>10</v>
       </c>
       <c r="AG35" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="2:33" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B36" s="4">
         <v>1</v>
       </c>
@@ -1727,7 +1727,7 @@
       <c r="AB36" s="4">
         <v>0</v>
       </c>
-      <c r="AC36" s="20">
+      <c r="AC36" s="6">
         <v>1</v>
       </c>
       <c r="AD36" s="4">
@@ -1736,14 +1736,14 @@
       <c r="AE36" s="4">
         <v>0</v>
       </c>
-      <c r="AF36" s="20">
+      <c r="AF36" s="6">
         <v>1</v>
       </c>
       <c r="AG36" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B37" s="4">
         <v>31</v>
       </c>
@@ -1843,6 +1843,20 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="Y3:AA3"/>
+    <mergeCell ref="AB3:AD3"/>
+    <mergeCell ref="AE3:AG3"/>
+    <mergeCell ref="J2:AG2"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="S3:U3"/>
+    <mergeCell ref="V3:X3"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="C33:C35"/>
     <mergeCell ref="D33:I33"/>
@@ -1857,20 +1871,6 @@
     <mergeCell ref="Y34:AA34"/>
     <mergeCell ref="AB34:AD34"/>
     <mergeCell ref="AE34:AG34"/>
-    <mergeCell ref="Y3:AA3"/>
-    <mergeCell ref="AB3:AD3"/>
-    <mergeCell ref="AE3:AG3"/>
-    <mergeCell ref="J2:AG2"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="S3:U3"/>
-    <mergeCell ref="V3:X3"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
